--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
@@ -994,7 +994,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1004,12 +1004,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1059,17 +1053,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
@@ -940,7 +940,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -5747,7 +5747,7 @@
         <v>67</v>
       </c>
       <c r="D104" s="7">
-        <v>1.5445</v>
+        <v>1.54445</v>
       </c>
       <c r="E104" s="6">
         <v>5992.05</v>
@@ -5767,7 +5767,7 @@
         <v>14</v>
       </c>
       <c r="D105" s="7">
-        <v>1.7042</v>
+        <v>1.704238</v>
       </c>
       <c r="E105" s="6">
         <v>1348.24</v>
@@ -5787,7 +5787,7 @@
         <v>8</v>
       </c>
       <c r="D106" s="7">
-        <v>1.7068</v>
+        <v>1.706812</v>
       </c>
       <c r="E106" s="6">
         <v>1066.45</v>
@@ -5807,7 +5807,7 @@
         <v>5</v>
       </c>
       <c r="D107" s="7">
-        <v>1.4331</v>
+        <v>1.433101</v>
       </c>
       <c r="E107" s="6">
         <v>250.42</v>
@@ -5827,7 +5827,7 @@
         <v>3</v>
       </c>
       <c r="D108" s="7">
-        <v>1.2489</v>
+        <v>1.248895</v>
       </c>
       <c r="E108" s="6">
         <v>42.4</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ/ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="306">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -942,8 +939,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1036,10 +1033,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1334,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1347,13 +1344,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1396,2616 +1393,2448 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2">
         <v>41.609</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H2">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I2" s="1">
-        <v>1.429</v>
+        <v>59.459</v>
       </c>
       <c r="J2">
-        <v>59.459261</v>
+        <v>1.51</v>
       </c>
       <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>62.82959</v>
-      </c>
-      <c r="M2" t="s">
-        <v>112</v>
-      </c>
-      <c r="N2">
+        <v>62.83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F3">
         <v>76.94</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H3">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I3" s="1">
-        <v>1.429</v>
+        <v>109.947</v>
       </c>
       <c r="J3">
-        <v>109.94726</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>116.1794</v>
-      </c>
-      <c r="M3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N3">
+        <v>116.179</v>
+      </c>
+      <c r="L3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F4">
         <v>37.43</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H4">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I4" s="1">
-        <v>1.429</v>
+        <v>53.487</v>
       </c>
       <c r="J4">
-        <v>53.48747</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>56.5193</v>
-      </c>
-      <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4">
+        <v>56.519</v>
+      </c>
+      <c r="L4" t="s">
+        <v>113</v>
+      </c>
+      <c r="M4">
         <v>305020</v>
       </c>
-      <c r="O4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F5">
         <v>62.219</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I5" s="1">
-        <v>1.429</v>
+        <v>88.911</v>
       </c>
       <c r="J5">
-        <v>88.910951</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>93.95068999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>115</v>
-      </c>
-      <c r="N5">
+        <v>93.95099999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5">
         <v>3339785</v>
       </c>
-      <c r="O5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F6">
         <v>51.397</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H6">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I6" s="1">
-        <v>1.429</v>
+        <v>73.446</v>
       </c>
       <c r="J6">
-        <v>73.446313</v>
+        <v>1.51</v>
       </c>
       <c r="K6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L6" s="1">
-        <v>77.60947</v>
-      </c>
-      <c r="M6" t="s">
-        <v>116</v>
-      </c>
-      <c r="N6">
+        <v>77.60899999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F7">
         <v>142.033</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H7">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I7" s="1">
-        <v>1.429</v>
+        <v>202.965</v>
       </c>
       <c r="J7">
-        <v>202.965157</v>
+        <v>1.51</v>
       </c>
       <c r="K7" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L7" s="1">
-        <v>214.46983</v>
-      </c>
-      <c r="M7" t="s">
-        <v>117</v>
-      </c>
-      <c r="N7">
+        <v>214.47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F8">
         <v>26.877</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I8" s="1">
-        <v>1.429</v>
+        <v>38.407</v>
       </c>
       <c r="J8">
-        <v>38.407233</v>
+        <v>1.55</v>
       </c>
       <c r="K8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L8" s="1">
-        <v>41.65935</v>
-      </c>
-      <c r="M8" t="s">
-        <v>118</v>
-      </c>
-      <c r="N8">
+        <v>41.659</v>
+      </c>
+      <c r="L8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F9">
         <v>63.633</v>
       </c>
       <c r="G9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H9">
-        <v>1.649</v>
+        <v>1.709</v>
       </c>
       <c r="I9" s="1">
-        <v>1.709</v>
+        <v>108.749</v>
       </c>
       <c r="J9">
-        <v>108.748797</v>
+        <v>1.77</v>
       </c>
       <c r="K9" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L9" s="1">
-        <v>112.63041</v>
-      </c>
-      <c r="M9" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9">
+        <v>112.63</v>
+      </c>
+      <c r="L9" t="s">
+        <v>118</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F10">
         <v>36.822</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I10" s="1">
-        <v>1.429</v>
+        <v>52.619</v>
       </c>
       <c r="J10">
-        <v>52.618638</v>
+        <v>1.52</v>
       </c>
       <c r="K10" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L10" s="1">
-        <v>55.96944</v>
-      </c>
-      <c r="M10" t="s">
-        <v>120</v>
-      </c>
-      <c r="N10">
+        <v>55.969</v>
+      </c>
+      <c r="L10" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10">
         <v>413405</v>
       </c>
-      <c r="O10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11">
         <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H11">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I11" s="1">
-        <v>1.679</v>
+        <v>75.55500000000001</v>
       </c>
       <c r="J11">
-        <v>75.55500000000001</v>
+        <v>1.78</v>
       </c>
       <c r="K11" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L11" s="1">
         <v>80.09999999999999</v>
       </c>
-      <c r="M11" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F12">
         <v>75.131</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H12">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I12" s="1">
-        <v>1.689</v>
+        <v>126.896</v>
       </c>
       <c r="J12">
-        <v>126.896259</v>
+        <v>1.76</v>
       </c>
       <c r="K12" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L12" s="1">
-        <v>132.23056</v>
-      </c>
-      <c r="M12" t="s">
-        <v>122</v>
-      </c>
-      <c r="N12">
+        <v>132.231</v>
+      </c>
+      <c r="L12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F13">
         <v>42.433</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H13">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I13" s="1">
-        <v>1.679</v>
+        <v>71.245</v>
       </c>
       <c r="J13">
-        <v>71.245007</v>
+        <v>1.78</v>
       </c>
       <c r="K13" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L13" s="1">
-        <v>75.53073999999999</v>
-      </c>
-      <c r="M13" t="s">
-        <v>123</v>
-      </c>
-      <c r="N13">
+        <v>75.53100000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>122</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F14">
         <v>38.77</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H14">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I14" s="1">
-        <v>1.436</v>
+        <v>55.674</v>
       </c>
       <c r="J14">
-        <v>55.67372</v>
+        <v>1.52</v>
       </c>
       <c r="K14" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L14" s="1">
-        <v>58.9304</v>
-      </c>
-      <c r="M14" t="s">
-        <v>124</v>
-      </c>
-      <c r="N14">
+        <v>58.93</v>
+      </c>
+      <c r="L14" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14">
         <v>305332</v>
       </c>
-      <c r="O14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F15">
         <v>105.559</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H15">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I15" s="1">
-        <v>1.436</v>
+        <v>151.583</v>
       </c>
       <c r="J15">
-        <v>151.582724</v>
+        <v>1.52</v>
       </c>
       <c r="K15" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L15" s="1">
-        <v>160.44968</v>
-      </c>
-      <c r="M15" t="s">
-        <v>125</v>
-      </c>
-      <c r="N15">
+        <v>160.45</v>
+      </c>
+      <c r="L15" t="s">
+        <v>124</v>
+      </c>
+      <c r="M15">
         <v>121878</v>
       </c>
-      <c r="O15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16">
         <v>70.307</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H16">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I16" s="1">
-        <v>1.436</v>
+        <v>100.961</v>
       </c>
       <c r="J16">
-        <v>100.960852</v>
+        <v>1.53</v>
       </c>
       <c r="K16" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L16" s="1">
-        <v>107.56971</v>
-      </c>
-      <c r="M16" t="s">
-        <v>126</v>
-      </c>
-      <c r="N16">
+        <v>107.57</v>
+      </c>
+      <c r="L16" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16">
         <v>341360</v>
       </c>
-      <c r="O16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F17">
         <v>25.84</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H17">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I17" s="1">
-        <v>1.389</v>
+        <v>35.892</v>
       </c>
       <c r="J17">
-        <v>35.89176</v>
+        <v>1.5</v>
       </c>
       <c r="K17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L17" s="1">
         <v>38.76</v>
       </c>
-      <c r="M17" t="s">
-        <v>127</v>
-      </c>
-      <c r="N17">
+      <c r="L17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17">
         <v>16400</v>
       </c>
-      <c r="O17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F18">
         <v>36.797</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H18">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I18" s="1">
-        <v>1.436</v>
+        <v>52.84</v>
       </c>
       <c r="J18">
-        <v>52.840492</v>
+        <v>1.53</v>
       </c>
       <c r="K18" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L18" s="1">
-        <v>56.29941</v>
-      </c>
-      <c r="M18" t="s">
-        <v>128</v>
-      </c>
-      <c r="N18">
+        <v>56.299</v>
+      </c>
+      <c r="L18" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18">
         <v>382491</v>
       </c>
-      <c r="O18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F19">
         <v>72.56699999999999</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H19">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I19" s="1">
-        <v>1.679</v>
+        <v>121.84</v>
       </c>
       <c r="J19">
-        <v>121.839993</v>
+        <v>1.78</v>
       </c>
       <c r="K19" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L19" s="1">
-        <v>129.16926</v>
-      </c>
-      <c r="M19" t="s">
-        <v>129</v>
-      </c>
-      <c r="N19">
+        <v>129.169</v>
+      </c>
+      <c r="L19" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19">
         <v>0</v>
       </c>
-      <c r="O19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F20">
         <v>90.313</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H20">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I20" s="1">
-        <v>1.689</v>
+        <v>152.539</v>
       </c>
       <c r="J20">
-        <v>152.538657</v>
+        <v>1.76</v>
       </c>
       <c r="K20" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L20" s="1">
-        <v>158.95088</v>
-      </c>
-      <c r="M20" t="s">
-        <v>130</v>
-      </c>
-      <c r="N20">
+        <v>158.951</v>
+      </c>
+      <c r="L20" t="s">
+        <v>129</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21">
         <v>128.897</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H21">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I21" s="1">
-        <v>1.436</v>
+        <v>185.096</v>
       </c>
       <c r="J21">
-        <v>185.096092</v>
+        <v>1.56</v>
       </c>
       <c r="K21" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L21" s="1">
-        <v>201.07932</v>
-      </c>
-      <c r="M21" t="s">
-        <v>131</v>
-      </c>
-      <c r="N21">
+        <v>201.079</v>
+      </c>
+      <c r="L21" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21">
         <v>0</v>
       </c>
-      <c r="O21" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F22">
         <v>59.671</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H22">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I22" s="1">
-        <v>1.442</v>
+        <v>86.04600000000001</v>
       </c>
       <c r="J22">
-        <v>86.045582</v>
+        <v>1.52</v>
       </c>
       <c r="K22" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L22" s="1">
-        <v>90.69992000000001</v>
-      </c>
-      <c r="M22" t="s">
-        <v>132</v>
-      </c>
-      <c r="N22">
+        <v>90.7</v>
+      </c>
+      <c r="L22" t="s">
+        <v>131</v>
+      </c>
+      <c r="M22">
         <v>364870</v>
       </c>
-      <c r="O22" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23">
         <v>78</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H23">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I23" s="1">
-        <v>1.442</v>
+        <v>112.476</v>
       </c>
       <c r="J23">
-        <v>112.476</v>
+        <v>1.52</v>
       </c>
       <c r="K23" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L23" s="1">
         <v>118.56</v>
       </c>
-      <c r="M23" t="s">
-        <v>133</v>
-      </c>
-      <c r="N23">
+      <c r="L23" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23">
         <v>0</v>
       </c>
-      <c r="O23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24">
         <v>40.268</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H24">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I24" s="1">
-        <v>1.389</v>
+        <v>55.932</v>
       </c>
       <c r="J24">
-        <v>55.932252</v>
+        <v>1.49</v>
       </c>
       <c r="K24" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L24" s="1">
-        <v>59.99932</v>
-      </c>
-      <c r="M24" t="s">
-        <v>134</v>
-      </c>
-      <c r="N24">
+        <v>59.999</v>
+      </c>
+      <c r="L24" t="s">
+        <v>133</v>
+      </c>
+      <c r="M24">
         <v>15803</v>
       </c>
-      <c r="O24" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25">
         <v>52.111</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H25">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I25" s="1">
-        <v>1.442</v>
+        <v>75.14400000000001</v>
       </c>
       <c r="J25">
-        <v>75.14406200000001</v>
+        <v>1.53</v>
       </c>
       <c r="K25" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L25" s="1">
-        <v>79.72983000000001</v>
-      </c>
-      <c r="M25" t="s">
-        <v>135</v>
-      </c>
-      <c r="N25">
+        <v>79.73</v>
+      </c>
+      <c r="L25" t="s">
+        <v>134</v>
+      </c>
+      <c r="M25">
         <v>340800</v>
       </c>
-      <c r="O25" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F26">
         <v>45.039</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H26">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I26" s="1">
-        <v>1.442</v>
+        <v>64.946</v>
       </c>
       <c r="J26">
-        <v>64.94623799999999</v>
+        <v>1.52</v>
       </c>
       <c r="K26" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L26" s="1">
-        <v>68.45928000000001</v>
-      </c>
-      <c r="M26" t="s">
-        <v>136</v>
-      </c>
-      <c r="N26">
+        <v>68.459</v>
+      </c>
+      <c r="L26" t="s">
+        <v>135</v>
+      </c>
+      <c r="M26">
         <v>872228</v>
       </c>
-      <c r="O26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27">
         <v>59.079</v>
       </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H27">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I27" s="1">
-        <v>1.442</v>
+        <v>85.19199999999999</v>
       </c>
       <c r="J27">
-        <v>85.191918</v>
+        <v>1.52</v>
       </c>
       <c r="K27" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L27" s="1">
-        <v>89.80007999999999</v>
-      </c>
-      <c r="M27" t="s">
-        <v>137</v>
-      </c>
-      <c r="N27">
+        <v>89.8</v>
+      </c>
+      <c r="L27" t="s">
+        <v>136</v>
+      </c>
+      <c r="M27">
         <v>0</v>
       </c>
-      <c r="O27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F28">
         <v>38.848</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H28">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I28" s="1">
-        <v>1.442</v>
+        <v>56.019</v>
       </c>
       <c r="J28">
-        <v>56.018816</v>
+        <v>1.51</v>
       </c>
       <c r="K28" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L28" s="1">
-        <v>58.66048</v>
-      </c>
-      <c r="M28" t="s">
-        <v>138</v>
-      </c>
-      <c r="N28">
+        <v>58.66</v>
+      </c>
+      <c r="L28" t="s">
+        <v>137</v>
+      </c>
+      <c r="M28">
         <v>826676</v>
       </c>
-      <c r="O28" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F29">
         <v>57.987</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H29">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I29" s="1">
-        <v>1.442</v>
+        <v>83.617</v>
       </c>
       <c r="J29">
-        <v>83.617254</v>
+        <v>1.52</v>
       </c>
       <c r="K29" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L29" s="1">
-        <v>88.14024000000001</v>
-      </c>
-      <c r="M29" t="s">
-        <v>139</v>
-      </c>
-      <c r="N29">
+        <v>88.14</v>
+      </c>
+      <c r="L29" t="s">
+        <v>138</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30">
         <v>89.408</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H30">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I30" s="1">
-        <v>1.442</v>
+        <v>128.926</v>
       </c>
       <c r="J30">
-        <v>128.926336</v>
+        <v>1.52</v>
       </c>
       <c r="K30" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L30" s="1">
-        <v>135.90016</v>
-      </c>
-      <c r="M30" t="s">
-        <v>140</v>
-      </c>
-      <c r="N30">
+        <v>135.9</v>
+      </c>
+      <c r="L30" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30">
         <v>123264</v>
       </c>
-      <c r="O30" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F31">
         <v>28.577</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H31">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I31" s="1">
-        <v>1.442</v>
+        <v>41.208</v>
       </c>
       <c r="J31">
-        <v>41.208034</v>
+        <v>1.56</v>
       </c>
       <c r="K31" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L31" s="1">
-        <v>44.58012</v>
-      </c>
-      <c r="M31" t="s">
-        <v>141</v>
-      </c>
-      <c r="N31">
+        <v>44.58</v>
+      </c>
+      <c r="L31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31">
         <v>0</v>
       </c>
-      <c r="O31" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32">
         <v>44.239</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H32">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I32" s="1">
-        <v>1.679</v>
+        <v>74.277</v>
       </c>
       <c r="J32">
-        <v>74.277281</v>
+        <v>1.8</v>
       </c>
       <c r="K32" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L32" s="1">
-        <v>79.6302</v>
-      </c>
-      <c r="M32" t="s">
-        <v>138</v>
-      </c>
-      <c r="N32">
+        <v>79.63</v>
+      </c>
+      <c r="L32" t="s">
+        <v>137</v>
+      </c>
+      <c r="M32">
         <v>0</v>
       </c>
-      <c r="O32" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F33">
         <v>38.929</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H33">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I33" s="1">
-        <v>1.467</v>
+        <v>57.109</v>
       </c>
       <c r="J33">
-        <v>57.108843</v>
+        <v>1.54</v>
       </c>
       <c r="K33" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L33" s="1">
-        <v>59.95066</v>
-      </c>
-      <c r="M33" t="s">
-        <v>142</v>
-      </c>
-      <c r="N33">
+        <v>59.951</v>
+      </c>
+      <c r="L33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M33">
         <v>306095</v>
       </c>
-      <c r="O33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F34">
         <v>35.071</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H34">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I34" s="1">
-        <v>1.467</v>
+        <v>51.449</v>
       </c>
       <c r="J34">
-        <v>51.449157</v>
+        <v>1.55</v>
       </c>
       <c r="K34" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L34" s="1">
-        <v>54.36005</v>
-      </c>
-      <c r="M34" t="s">
-        <v>143</v>
-      </c>
-      <c r="N34">
+        <v>54.36</v>
+      </c>
+      <c r="L34" t="s">
+        <v>142</v>
+      </c>
+      <c r="M34">
         <v>382904</v>
       </c>
-      <c r="O34" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35">
         <v>59.712</v>
       </c>
       <c r="G35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H35">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I35" s="1">
-        <v>1.481</v>
+        <v>88.43300000000001</v>
       </c>
       <c r="J35">
-        <v>88.43347199999999</v>
+        <v>1.56</v>
       </c>
       <c r="K35" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L35" s="1">
-        <v>93.15072000000001</v>
-      </c>
-      <c r="M35" t="s">
-        <v>144</v>
-      </c>
-      <c r="N35">
+        <v>93.151</v>
+      </c>
+      <c r="L35" t="s">
+        <v>143</v>
+      </c>
+      <c r="M35">
         <v>455475</v>
       </c>
-      <c r="O35" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F36">
         <v>51.462</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H36">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I36" s="1">
-        <v>1.481</v>
+        <v>76.215</v>
       </c>
       <c r="J36">
-        <v>76.215222</v>
+        <v>1.58</v>
       </c>
       <c r="K36" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L36" s="1">
-        <v>81.30996</v>
-      </c>
-      <c r="M36" t="s">
-        <v>145</v>
-      </c>
-      <c r="N36">
+        <v>81.31</v>
+      </c>
+      <c r="L36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M36">
         <v>0</v>
       </c>
-      <c r="O36" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F37">
         <v>69.571</v>
       </c>
       <c r="G37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H37">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I37" s="1">
-        <v>1.689</v>
+        <v>117.505</v>
       </c>
       <c r="J37">
-        <v>117.505419</v>
+        <v>1.75</v>
       </c>
       <c r="K37" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L37" s="1">
-        <v>121.74925</v>
-      </c>
-      <c r="M37" t="s">
-        <v>146</v>
-      </c>
-      <c r="N37">
+        <v>121.749</v>
+      </c>
+      <c r="L37" t="s">
+        <v>145</v>
+      </c>
+      <c r="M37">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F38">
         <v>60.102</v>
       </c>
       <c r="G38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H38">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I38" s="1">
-        <v>1.481</v>
+        <v>89.011</v>
       </c>
       <c r="J38">
-        <v>89.011062</v>
+        <v>1.57</v>
       </c>
       <c r="K38" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="L38" s="1">
-        <v>94.36014</v>
-      </c>
-      <c r="M38" t="s">
-        <v>147</v>
-      </c>
-      <c r="N38">
+        <v>94.36</v>
+      </c>
+      <c r="L38" t="s">
+        <v>146</v>
+      </c>
+      <c r="M38">
         <v>341317</v>
       </c>
-      <c r="O38" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F39">
         <v>55</v>
       </c>
       <c r="G39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H39">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I39" s="1">
-        <v>1.679</v>
+        <v>92.345</v>
       </c>
       <c r="J39">
-        <v>92.345</v>
+        <v>1.82</v>
       </c>
       <c r="K39" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L39" s="1">
         <v>100.1</v>
       </c>
-      <c r="M39" t="s">
-        <v>148</v>
-      </c>
-      <c r="N39">
+      <c r="L39" t="s">
+        <v>147</v>
+      </c>
+      <c r="M39">
         <v>298518</v>
       </c>
-      <c r="O39" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F40">
         <v>62.442</v>
       </c>
       <c r="G40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H40">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I40" s="1">
-        <v>1.499</v>
+        <v>93.601</v>
       </c>
       <c r="J40">
-        <v>93.60055800000001</v>
+        <v>1.56</v>
       </c>
       <c r="K40" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L40" s="1">
-        <v>97.40952</v>
-      </c>
-      <c r="M40" t="s">
-        <v>149</v>
-      </c>
-      <c r="N40">
+        <v>97.41</v>
+      </c>
+      <c r="L40" t="s">
+        <v>148</v>
+      </c>
+      <c r="M40">
         <v>0</v>
       </c>
-      <c r="O40" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F41">
         <v>53.038</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H41">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I41" s="1">
-        <v>1.679</v>
+        <v>89.051</v>
       </c>
       <c r="J41">
-        <v>89.050802</v>
+        <v>1.82</v>
       </c>
       <c r="K41" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L41" s="1">
-        <v>96.52916</v>
-      </c>
-      <c r="M41" t="s">
-        <v>150</v>
-      </c>
-      <c r="N41">
+        <v>96.529</v>
+      </c>
+      <c r="L41" t="s">
+        <v>149</v>
+      </c>
+      <c r="M41">
         <v>365182</v>
       </c>
-      <c r="O41" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42">
         <v>8.606</v>
       </c>
       <c r="G42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H42">
         <v>1.27</v>
       </c>
       <c r="I42" s="1">
+        <v>10.93</v>
+      </c>
+      <c r="J42">
         <v>1.27</v>
       </c>
-      <c r="J42">
-        <v>10.92962</v>
-      </c>
       <c r="K42" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="L42" s="1">
-        <v>10.92962</v>
-      </c>
-      <c r="M42" t="s">
-        <v>151</v>
-      </c>
-      <c r="N42">
+        <v>10.93</v>
+      </c>
+      <c r="L42" t="s">
+        <v>150</v>
+      </c>
+      <c r="M42">
         <v>873623</v>
       </c>
-      <c r="O42" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F43">
         <v>47.283</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H43">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I43" s="1">
-        <v>1.499</v>
+        <v>70.877</v>
       </c>
       <c r="J43">
-        <v>70.877217</v>
+        <v>1.59</v>
       </c>
       <c r="K43" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="L43" s="1">
-        <v>75.17997</v>
-      </c>
-      <c r="M43" t="s">
-        <v>152</v>
-      </c>
-      <c r="N43">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="L43" t="s">
+        <v>151</v>
+      </c>
+      <c r="M43">
         <v>873623</v>
       </c>
-      <c r="O43" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44">
         <v>55.804</v>
       </c>
       <c r="G44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H44">
-        <v>1.489</v>
+        <v>1.519</v>
       </c>
       <c r="I44" s="1">
-        <v>1.519</v>
+        <v>84.76600000000001</v>
       </c>
       <c r="J44">
-        <v>84.766276</v>
+        <v>1.58</v>
       </c>
       <c r="K44" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L44" s="1">
-        <v>88.17032</v>
-      </c>
-      <c r="M44" t="s">
-        <v>153</v>
-      </c>
-      <c r="N44">
+        <v>88.17</v>
+      </c>
+      <c r="L44" t="s">
+        <v>152</v>
+      </c>
+      <c r="M44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F45">
         <v>75.203</v>
       </c>
       <c r="G45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H45">
-        <v>1.489</v>
+        <v>1.519</v>
       </c>
       <c r="I45" s="1">
-        <v>1.519</v>
+        <v>114.233</v>
       </c>
       <c r="J45">
-        <v>114.233357</v>
+        <v>1.58</v>
       </c>
       <c r="K45" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L45" s="1">
-        <v>118.82074</v>
-      </c>
-      <c r="M45" t="s">
-        <v>154</v>
-      </c>
-      <c r="N45">
+        <v>118.821</v>
+      </c>
+      <c r="L45" t="s">
+        <v>153</v>
+      </c>
+      <c r="M45">
         <v>873919</v>
       </c>
-      <c r="O45" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46">
         <v>77</v>
       </c>
       <c r="G46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H46">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I46" s="1">
-        <v>1.679</v>
+        <v>129.283</v>
       </c>
       <c r="J46">
-        <v>129.283</v>
+        <v>1.84</v>
       </c>
       <c r="K46" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="L46" s="1">
         <v>141.68</v>
       </c>
-      <c r="M46" t="s">
-        <v>155</v>
-      </c>
-      <c r="N46">
+      <c r="L46" t="s">
+        <v>154</v>
+      </c>
+      <c r="M46">
         <v>0</v>
       </c>
-      <c r="O46" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47">
         <v>53.89</v>
       </c>
       <c r="G47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H47">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I47" s="1">
-        <v>1.529</v>
+        <v>82.398</v>
       </c>
       <c r="J47">
-        <v>82.39781000000001</v>
+        <v>1.64</v>
       </c>
       <c r="K47" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="L47" s="1">
-        <v>88.3796</v>
-      </c>
-      <c r="M47" t="s">
-        <v>156</v>
-      </c>
-      <c r="N47">
+        <v>88.38</v>
+      </c>
+      <c r="L47" t="s">
+        <v>155</v>
+      </c>
+      <c r="M47">
         <v>0</v>
       </c>
-      <c r="O47" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F48">
         <v>100.217</v>
       </c>
       <c r="G48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H48">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I48" s="1">
-        <v>1.529</v>
+        <v>153.232</v>
       </c>
       <c r="J48">
-        <v>153.231793</v>
+        <v>1.61</v>
       </c>
       <c r="K48" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L48" s="1">
-        <v>161.34937</v>
-      </c>
-      <c r="M48" t="s">
-        <v>157</v>
-      </c>
-      <c r="N48">
+        <v>161.349</v>
+      </c>
+      <c r="L48" t="s">
+        <v>156</v>
+      </c>
+      <c r="M48">
         <v>0</v>
       </c>
-      <c r="O48" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F49">
         <v>57.802</v>
       </c>
       <c r="G49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H49">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I49" s="1">
-        <v>1.529</v>
+        <v>88.379</v>
       </c>
       <c r="J49">
-        <v>88.37925799999999</v>
+        <v>1.62</v>
       </c>
       <c r="K49" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L49" s="1">
-        <v>93.63924</v>
-      </c>
-      <c r="M49" t="s">
-        <v>158</v>
-      </c>
-      <c r="N49">
+        <v>93.639</v>
+      </c>
+      <c r="L49" t="s">
+        <v>157</v>
+      </c>
+      <c r="M49">
         <v>341795</v>
       </c>
-      <c r="O49" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F50">
         <v>29.957</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H50">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I50" s="1">
-        <v>1.529</v>
+        <v>45.804</v>
       </c>
       <c r="J50">
-        <v>45.804253</v>
+        <v>1.64</v>
       </c>
       <c r="K50" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="L50" s="1">
-        <v>49.12948</v>
-      </c>
-      <c r="M50" t="s">
-        <v>159</v>
-      </c>
-      <c r="N50">
+        <v>49.129</v>
+      </c>
+      <c r="L50" t="s">
+        <v>158</v>
+      </c>
+      <c r="M50">
         <v>416008</v>
       </c>
-      <c r="O50" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F51">
         <v>51.258</v>
       </c>
       <c r="G51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H51">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I51" s="1">
-        <v>1.529</v>
+        <v>78.373</v>
       </c>
       <c r="J51">
-        <v>78.373482</v>
+        <v>1.63</v>
       </c>
       <c r="K51" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L51" s="1">
-        <v>83.55054</v>
-      </c>
-      <c r="M51" t="s">
-        <v>160</v>
-      </c>
-      <c r="N51">
+        <v>83.551</v>
+      </c>
+      <c r="L51" t="s">
+        <v>159</v>
+      </c>
+      <c r="M51">
         <v>455925</v>
       </c>
-      <c r="O51" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52">
         <v>46.072</v>
       </c>
       <c r="G52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H52">
-        <v>1.628</v>
+        <v>1.708</v>
       </c>
       <c r="I52" s="1">
-        <v>1.708</v>
+        <v>78.691</v>
       </c>
       <c r="J52">
-        <v>78.69097600000001</v>
+        <v>1.94</v>
       </c>
       <c r="K52" s="1">
-        <v>1.94</v>
-      </c>
-      <c r="L52" s="1">
-        <v>89.37967999999999</v>
-      </c>
-      <c r="M52" t="s">
-        <v>123</v>
-      </c>
-      <c r="N52">
+        <v>89.38</v>
+      </c>
+      <c r="L52" t="s">
+        <v>122</v>
+      </c>
+      <c r="M52">
         <v>0</v>
       </c>
-      <c r="O52" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F53">
         <v>64.97</v>
       </c>
       <c r="G53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H53">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I53" s="1">
-        <v>1.576</v>
+        <v>102.393</v>
       </c>
       <c r="J53">
-        <v>102.39272</v>
+        <v>1.68</v>
       </c>
       <c r="K53" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L53" s="1">
-        <v>109.1496</v>
-      </c>
-      <c r="M53" t="s">
-        <v>161</v>
-      </c>
-      <c r="N53">
+        <v>109.15</v>
+      </c>
+      <c r="L53" t="s">
+        <v>160</v>
+      </c>
+      <c r="M53">
         <v>365549</v>
       </c>
-      <c r="O53" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F54">
         <v>72.762</v>
       </c>
       <c r="G54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H54">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I54" s="1">
-        <v>1.594</v>
+        <v>115.983</v>
       </c>
       <c r="J54">
-        <v>115.982628</v>
+        <v>1.68</v>
       </c>
       <c r="K54" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L54" s="1">
-        <v>122.24016</v>
-      </c>
-      <c r="M54" t="s">
-        <v>162</v>
-      </c>
-      <c r="N54">
+        <v>122.24</v>
+      </c>
+      <c r="L54" t="s">
+        <v>161</v>
+      </c>
+      <c r="M54">
         <v>874713</v>
       </c>
-      <c r="O54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="N54" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55">
         <v>57.131</v>
       </c>
       <c r="G55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H55">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I55" s="1">
-        <v>1.594</v>
+        <v>91.06699999999999</v>
       </c>
       <c r="J55">
-        <v>91.06681399999999</v>
+        <v>1.68</v>
       </c>
       <c r="K55" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L55" s="1">
-        <v>95.98008</v>
-      </c>
-      <c r="M55" t="s">
-        <v>163</v>
-      </c>
-      <c r="N55">
+        <v>95.98</v>
+      </c>
+      <c r="L55" t="s">
+        <v>162</v>
+      </c>
+      <c r="M55">
         <v>0</v>
       </c>
-      <c r="O55" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="N55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F56">
         <v>62.589</v>
       </c>
       <c r="G56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H56">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I56" s="1">
-        <v>1.594</v>
+        <v>99.767</v>
       </c>
       <c r="J56">
-        <v>99.76686599999999</v>
+        <v>1.68</v>
       </c>
       <c r="K56" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L56" s="1">
-        <v>105.14952</v>
-      </c>
-      <c r="M56" t="s">
-        <v>164</v>
-      </c>
-      <c r="N56">
+        <v>105.15</v>
+      </c>
+      <c r="L56" t="s">
+        <v>163</v>
+      </c>
+      <c r="M56">
         <v>0</v>
       </c>
-      <c r="O56" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="N56" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H57">
         <v>10.39</v>
@@ -4019,1996 +3848,1867 @@
       <c r="K57" s="1">
         <v>10.39</v>
       </c>
-      <c r="L57" s="1">
-        <v>10.39</v>
-      </c>
-      <c r="M57" t="s">
-        <v>165</v>
-      </c>
-      <c r="N57">
+      <c r="L57" t="s">
+        <v>164</v>
+      </c>
+      <c r="M57">
         <v>0</v>
       </c>
-      <c r="O57" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="N57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F58">
         <v>65.97199999999999</v>
       </c>
       <c r="G58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H58">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I58" s="1">
-        <v>1.689</v>
+        <v>111.427</v>
       </c>
       <c r="J58">
-        <v>111.426708</v>
+        <v>1.79</v>
       </c>
       <c r="K58" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L58" s="1">
-        <v>118.08988</v>
-      </c>
-      <c r="M58" t="s">
-        <v>166</v>
-      </c>
-      <c r="N58">
+        <v>118.09</v>
+      </c>
+      <c r="L58" t="s">
+        <v>165</v>
+      </c>
+      <c r="M58">
         <v>0</v>
       </c>
-      <c r="O58" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="N58" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59">
         <v>59.651</v>
       </c>
       <c r="G59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H59">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I59" s="1">
-        <v>1.594</v>
+        <v>95.084</v>
       </c>
       <c r="J59">
-        <v>95.08369399999999</v>
+        <v>1.69</v>
       </c>
       <c r="K59" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100.81019</v>
-      </c>
-      <c r="M59" t="s">
-        <v>167</v>
-      </c>
-      <c r="N59">
+        <v>100.81</v>
+      </c>
+      <c r="L59" t="s">
+        <v>166</v>
+      </c>
+      <c r="M59">
         <v>342277</v>
       </c>
-      <c r="O59" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="N59" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F60">
         <v>146.789</v>
       </c>
       <c r="G60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H60">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I60" s="1">
-        <v>1.594</v>
+        <v>233.982</v>
       </c>
       <c r="J60">
-        <v>233.981666</v>
+        <v>1.71</v>
       </c>
       <c r="K60" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L60" s="1">
-        <v>251.00919</v>
-      </c>
-      <c r="M60" t="s">
-        <v>168</v>
-      </c>
-      <c r="N60">
+        <v>251.009</v>
+      </c>
+      <c r="L60" t="s">
+        <v>167</v>
+      </c>
+      <c r="M60">
         <v>0</v>
       </c>
-      <c r="O60" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="N60" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F61">
         <v>36.987</v>
       </c>
       <c r="G61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H61">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I61" s="1">
-        <v>1.441</v>
+        <v>53.298</v>
       </c>
       <c r="J61">
-        <v>53.298267</v>
+        <v>1.54</v>
       </c>
       <c r="K61" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L61" s="1">
-        <v>56.95998</v>
-      </c>
-      <c r="M61" t="s">
-        <v>169</v>
-      </c>
-      <c r="N61">
+        <v>56.96</v>
+      </c>
+      <c r="L61" t="s">
+        <v>168</v>
+      </c>
+      <c r="M61">
         <v>0</v>
       </c>
-      <c r="O61" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="N61" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F62">
         <v>50</v>
       </c>
       <c r="G62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H62">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I62" s="1">
-        <v>1.728</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J62">
-        <v>86.40000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="K62" s="1">
-        <v>1.95</v>
-      </c>
-      <c r="L62" s="1">
         <v>97.5</v>
       </c>
-      <c r="M62" t="s">
-        <v>170</v>
-      </c>
-      <c r="N62">
+      <c r="L62" t="s">
+        <v>169</v>
+      </c>
+      <c r="M62">
         <v>299022</v>
       </c>
-      <c r="O62" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="N62" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F63">
         <v>58.559</v>
       </c>
       <c r="G63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H63">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I63" s="1">
-        <v>1.618</v>
+        <v>94.748</v>
       </c>
       <c r="J63">
-        <v>94.748462</v>
+        <v>1.7</v>
       </c>
       <c r="K63" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L63" s="1">
-        <v>99.55029999999999</v>
-      </c>
-      <c r="M63" t="s">
-        <v>171</v>
-      </c>
-      <c r="N63">
+        <v>99.55</v>
+      </c>
+      <c r="L63" t="s">
+        <v>170</v>
+      </c>
+      <c r="M63">
         <v>0</v>
       </c>
-      <c r="O63" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="N63" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F64">
         <v>22.518</v>
       </c>
       <c r="G64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H64">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I64" s="1">
-        <v>1.618</v>
+        <v>36.434</v>
       </c>
       <c r="J64">
-        <v>36.434124</v>
+        <v>1.7</v>
       </c>
       <c r="K64" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L64" s="1">
-        <v>38.2806</v>
-      </c>
-      <c r="M64" t="s">
-        <v>172</v>
-      </c>
-      <c r="N64">
+        <v>38.281</v>
+      </c>
+      <c r="L64" t="s">
+        <v>171</v>
+      </c>
+      <c r="M64">
         <v>0</v>
       </c>
-      <c r="O64" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="N64" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F65">
         <v>78.212</v>
       </c>
       <c r="G65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H65">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I65" s="1">
-        <v>1.618</v>
+        <v>126.547</v>
       </c>
       <c r="J65">
-        <v>126.547016</v>
+        <v>1.7</v>
       </c>
       <c r="K65" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L65" s="1">
-        <v>132.9604</v>
-      </c>
-      <c r="M65" t="s">
-        <v>173</v>
-      </c>
-      <c r="N65">
+        <v>132.96</v>
+      </c>
+      <c r="L65" t="s">
+        <v>172</v>
+      </c>
+      <c r="M65">
         <v>0</v>
       </c>
-      <c r="O65" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="N65" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F66">
         <v>78.071</v>
       </c>
       <c r="G66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H66">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I66" s="1">
-        <v>1.728</v>
+        <v>134.907</v>
       </c>
       <c r="J66">
-        <v>134.906688</v>
+        <v>1.96</v>
       </c>
       <c r="K66" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="L66" s="1">
-        <v>153.01916</v>
-      </c>
-      <c r="M66" t="s">
-        <v>174</v>
-      </c>
-      <c r="N66">
+        <v>153.019</v>
+      </c>
+      <c r="L66" t="s">
+        <v>173</v>
+      </c>
+      <c r="M66">
         <v>0</v>
       </c>
-      <c r="O66" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="N66" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F67">
         <v>95.88200000000001</v>
       </c>
       <c r="G67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H67">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I67" s="1">
-        <v>1.618</v>
+        <v>155.137</v>
       </c>
       <c r="J67">
-        <v>155.137076</v>
+        <v>1.7</v>
       </c>
       <c r="K67" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L67" s="1">
-        <v>162.9994</v>
-      </c>
-      <c r="M67" t="s">
-        <v>175</v>
-      </c>
-      <c r="N67">
+        <v>162.999</v>
+      </c>
+      <c r="L67" t="s">
+        <v>174</v>
+      </c>
+      <c r="M67">
         <v>0</v>
       </c>
-      <c r="O67" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="N67" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F68">
         <v>94.8</v>
       </c>
       <c r="G68" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H68">
-        <v>1.649</v>
+        <v>1.709</v>
       </c>
       <c r="I68" s="1">
-        <v>1.709</v>
+        <v>162.013</v>
       </c>
       <c r="J68">
-        <v>162.0132</v>
+        <v>1.8</v>
       </c>
       <c r="K68" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L68" s="1">
         <v>170.64</v>
       </c>
-      <c r="M68" t="s">
-        <v>176</v>
-      </c>
-      <c r="N68">
+      <c r="L68" t="s">
+        <v>175</v>
+      </c>
+      <c r="M68">
         <v>0</v>
       </c>
-      <c r="O68" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="N68" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F69">
         <v>65.709</v>
       </c>
       <c r="G69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H69">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I69" s="1">
-        <v>1.728</v>
+        <v>113.545</v>
       </c>
       <c r="J69">
-        <v>113.545152</v>
+        <v>1.96</v>
       </c>
       <c r="K69" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="L69" s="1">
-        <v>128.78964</v>
-      </c>
-      <c r="M69" t="s">
-        <v>177</v>
-      </c>
-      <c r="N69">
+        <v>128.79</v>
+      </c>
+      <c r="L69" t="s">
+        <v>176</v>
+      </c>
+      <c r="M69">
         <v>0</v>
       </c>
-      <c r="O69" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="N69" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F70">
         <v>27.941</v>
       </c>
       <c r="G70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H70">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I70" s="1">
-        <v>1.618</v>
+        <v>45.209</v>
       </c>
       <c r="J70">
-        <v>45.208538</v>
+        <v>1.7</v>
       </c>
       <c r="K70" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L70" s="1">
-        <v>47.4997</v>
-      </c>
-      <c r="M70" t="s">
-        <v>178</v>
-      </c>
-      <c r="N70">
+        <v>47.5</v>
+      </c>
+      <c r="L70" t="s">
+        <v>177</v>
+      </c>
+      <c r="M70">
         <v>0</v>
       </c>
-      <c r="O70" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+      <c r="N70" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F71">
         <v>14.303</v>
       </c>
       <c r="G71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H71">
         <v>1.22</v>
       </c>
       <c r="I71" s="1">
+        <v>17.45</v>
+      </c>
+      <c r="J71">
         <v>1.22</v>
       </c>
-      <c r="J71">
-        <v>17.44966</v>
-      </c>
       <c r="K71" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L71" s="1">
-        <v>17.44966</v>
-      </c>
-      <c r="M71" t="s">
-        <v>178</v>
-      </c>
-      <c r="N71">
+        <v>17.45</v>
+      </c>
+      <c r="L71" t="s">
+        <v>177</v>
+      </c>
+      <c r="M71">
         <v>0</v>
       </c>
-      <c r="O71" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="N71" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F72">
         <v>78.459</v>
       </c>
       <c r="G72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H72">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I72" s="1">
-        <v>1.649</v>
+        <v>129.379</v>
       </c>
       <c r="J72">
-        <v>129.378891</v>
+        <v>1.72</v>
       </c>
       <c r="K72" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L72" s="1">
-        <v>134.94948</v>
-      </c>
-      <c r="M72" t="s">
-        <v>159</v>
-      </c>
-      <c r="N72">
+        <v>134.949</v>
+      </c>
+      <c r="L72" t="s">
+        <v>158</v>
+      </c>
+      <c r="M72">
         <v>875473</v>
       </c>
-      <c r="O72" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="N72" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F73">
         <v>48.75</v>
       </c>
       <c r="G73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H73">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I73" s="1">
-        <v>1.649</v>
+        <v>80.389</v>
       </c>
       <c r="J73">
-        <v>80.38875</v>
+        <v>1.72</v>
       </c>
       <c r="K73" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L73" s="1">
         <v>83.84999999999999</v>
       </c>
-      <c r="M73" t="s">
-        <v>179</v>
-      </c>
-      <c r="N73">
+      <c r="L73" t="s">
+        <v>178</v>
+      </c>
+      <c r="M73">
         <v>418905</v>
       </c>
-      <c r="O73" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
+      <c r="N73" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F74">
         <v>51.483</v>
       </c>
       <c r="G74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H74">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I74" s="1">
-        <v>1.649</v>
+        <v>84.895</v>
       </c>
       <c r="J74">
-        <v>84.895467</v>
+        <v>1.72</v>
       </c>
       <c r="K74" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L74" s="1">
-        <v>88.55076</v>
-      </c>
-      <c r="M74" t="s">
-        <v>180</v>
-      </c>
-      <c r="N74">
+        <v>88.551</v>
+      </c>
+      <c r="L74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M74">
         <v>342730</v>
       </c>
-      <c r="O74" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+      <c r="N74" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F75">
         <v>43.837</v>
       </c>
       <c r="G75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H75">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I75" s="1">
-        <v>1.649</v>
+        <v>72.28700000000001</v>
       </c>
       <c r="J75">
-        <v>72.28721299999999</v>
+        <v>1.72</v>
       </c>
       <c r="K75" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L75" s="1">
-        <v>75.39964000000001</v>
-      </c>
-      <c r="M75" t="s">
-        <v>181</v>
-      </c>
-      <c r="N75">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="L75" t="s">
+        <v>180</v>
+      </c>
+      <c r="M75">
         <v>0</v>
       </c>
-      <c r="O75" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+      <c r="N75" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F76">
         <v>29.839</v>
       </c>
       <c r="G76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H76">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I76" s="1">
-        <v>1.441</v>
+        <v>42.998</v>
       </c>
       <c r="J76">
-        <v>42.997999</v>
+        <v>1.55</v>
       </c>
       <c r="K76" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L76" s="1">
-        <v>46.25045</v>
-      </c>
-      <c r="M76" t="s">
-        <v>182</v>
-      </c>
-      <c r="N76">
+        <v>46.25</v>
+      </c>
+      <c r="L76" t="s">
+        <v>181</v>
+      </c>
+      <c r="M76">
         <v>0</v>
       </c>
-      <c r="O76" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+      <c r="N76" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F77">
         <v>51.269</v>
       </c>
       <c r="G77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H77">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I77" s="1">
-        <v>1.728</v>
+        <v>88.593</v>
       </c>
       <c r="J77">
-        <v>88.592832</v>
+        <v>2.01</v>
       </c>
       <c r="K77" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L77" s="1">
-        <v>103.05069</v>
-      </c>
-      <c r="M77" t="s">
-        <v>183</v>
-      </c>
-      <c r="N77">
+        <v>103.051</v>
+      </c>
+      <c r="L77" t="s">
+        <v>182</v>
+      </c>
+      <c r="M77">
         <v>0</v>
       </c>
-      <c r="O77" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
+      <c r="N77" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F78">
         <v>51.358</v>
       </c>
       <c r="G78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H78">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I78" s="1">
-        <v>1.728</v>
+        <v>88.747</v>
       </c>
       <c r="J78">
-        <v>88.746624</v>
+        <v>2.01</v>
       </c>
       <c r="K78" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L78" s="1">
-        <v>103.22958</v>
-      </c>
-      <c r="M78" t="s">
-        <v>138</v>
-      </c>
-      <c r="N78">
+        <v>103.23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>137</v>
+      </c>
+      <c r="M78">
         <v>0</v>
       </c>
-      <c r="O78" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
+      <c r="N78" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F79">
         <v>72.82299999999999</v>
       </c>
       <c r="G79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H79">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I79" s="1">
-        <v>1.649</v>
+        <v>120.085</v>
       </c>
       <c r="J79">
-        <v>120.085127</v>
+        <v>1.75</v>
       </c>
       <c r="K79" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L79" s="1">
-        <v>127.44025</v>
-      </c>
-      <c r="M79" t="s">
-        <v>170</v>
-      </c>
-      <c r="N79">
+        <v>127.44</v>
+      </c>
+      <c r="L79" t="s">
+        <v>169</v>
+      </c>
+      <c r="M79">
         <v>306360</v>
       </c>
-      <c r="O79" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15">
+      <c r="N79" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F80">
         <v>59.348</v>
       </c>
       <c r="G80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H80">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I80" s="1">
-        <v>1.728</v>
+        <v>102.553</v>
       </c>
       <c r="J80">
-        <v>102.553344</v>
+        <v>2.01</v>
       </c>
       <c r="K80" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L80" s="1">
-        <v>119.28948</v>
-      </c>
-      <c r="M80" t="s">
-        <v>184</v>
-      </c>
-      <c r="N80">
+        <v>119.289</v>
+      </c>
+      <c r="L80" t="s">
+        <v>183</v>
+      </c>
+      <c r="M80">
         <v>365919</v>
       </c>
-      <c r="O80" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+      <c r="N80" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F81">
         <v>50.909</v>
       </c>
       <c r="G81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H81">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I81" s="1">
-        <v>1.649</v>
+        <v>83.949</v>
       </c>
       <c r="J81">
-        <v>83.948941</v>
+        <v>1.75</v>
       </c>
       <c r="K81" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L81" s="1">
-        <v>89.09075</v>
-      </c>
-      <c r="M81" t="s">
-        <v>185</v>
-      </c>
-      <c r="N81">
+        <v>89.09099999999999</v>
+      </c>
+      <c r="L81" t="s">
+        <v>184</v>
+      </c>
+      <c r="M81">
         <v>0</v>
       </c>
-      <c r="O81" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
+      <c r="N81" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F82">
         <v>57.143</v>
       </c>
       <c r="G82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H82">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I82" s="1">
-        <v>1.683</v>
+        <v>96.172</v>
       </c>
       <c r="J82">
-        <v>96.17166899999999</v>
+        <v>1.75</v>
       </c>
       <c r="K82" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L82" s="1">
-        <v>100.00025</v>
-      </c>
-      <c r="M82" t="s">
-        <v>186</v>
-      </c>
-      <c r="N82">
+        <v>100</v>
+      </c>
+      <c r="L82" t="s">
+        <v>185</v>
+      </c>
+      <c r="M82">
         <v>0</v>
       </c>
-      <c r="O82" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+      <c r="N82" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F83">
         <v>64.45099999999999</v>
       </c>
       <c r="G83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H83">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I83" s="1">
-        <v>1.683</v>
+        <v>108.471</v>
       </c>
       <c r="J83">
-        <v>108.471033</v>
+        <v>1.75</v>
       </c>
       <c r="K83" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L83" s="1">
-        <v>112.78925</v>
-      </c>
-      <c r="M83" t="s">
-        <v>187</v>
-      </c>
-      <c r="N83">
+        <v>112.789</v>
+      </c>
+      <c r="L83" t="s">
+        <v>186</v>
+      </c>
+      <c r="M83">
         <v>0</v>
       </c>
-      <c r="O83" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+      <c r="N83" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F84">
         <v>93.45099999999999</v>
       </c>
       <c r="G84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H84">
-        <v>1.669</v>
+        <v>1.729</v>
       </c>
       <c r="I84" s="1">
-        <v>1.729</v>
+        <v>161.577</v>
       </c>
       <c r="J84">
-        <v>161.576779</v>
+        <v>1.82</v>
       </c>
       <c r="K84" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L84" s="1">
-        <v>170.08082</v>
-      </c>
-      <c r="M84" t="s">
-        <v>188</v>
-      </c>
-      <c r="N84">
+        <v>170.081</v>
+      </c>
+      <c r="L84" t="s">
+        <v>187</v>
+      </c>
+      <c r="M84">
         <v>0</v>
       </c>
-      <c r="O84" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="N84" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C85" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F85">
         <v>38.063</v>
       </c>
       <c r="G85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H85">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I85" s="1">
-        <v>1.683</v>
+        <v>64.06</v>
       </c>
       <c r="J85">
-        <v>64.060029</v>
+        <v>1.76</v>
       </c>
       <c r="K85" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L85" s="1">
-        <v>66.99088</v>
-      </c>
-      <c r="M85" t="s">
-        <v>189</v>
-      </c>
-      <c r="N85">
+        <v>66.991</v>
+      </c>
+      <c r="L85" t="s">
+        <v>188</v>
+      </c>
+      <c r="M85">
         <v>343052</v>
       </c>
-      <c r="O85" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
+      <c r="N85" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F86">
         <v>11.039</v>
       </c>
       <c r="G86" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H86">
         <v>1.27</v>
       </c>
       <c r="I86" s="1">
+        <v>14.02</v>
+      </c>
+      <c r="J86">
         <v>1.27</v>
       </c>
-      <c r="J86">
-        <v>14.01953</v>
-      </c>
       <c r="K86" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="L86" s="1">
-        <v>14.01953</v>
-      </c>
-      <c r="M86" t="s">
-        <v>190</v>
-      </c>
-      <c r="N86">
+        <v>14.02</v>
+      </c>
+      <c r="L86" t="s">
+        <v>189</v>
+      </c>
+      <c r="M86">
         <v>876348</v>
       </c>
-      <c r="O86" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+      <c r="N86" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E87" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F87">
         <v>49.81</v>
       </c>
       <c r="G87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H87">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I87" s="1">
-        <v>1.683</v>
+        <v>83.83</v>
       </c>
       <c r="J87">
-        <v>83.83023</v>
+        <v>1.79</v>
       </c>
       <c r="K87" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L87" s="1">
-        <v>89.15989999999999</v>
-      </c>
-      <c r="M87" t="s">
-        <v>191</v>
-      </c>
-      <c r="N87">
+        <v>89.16</v>
+      </c>
+      <c r="L87" t="s">
+        <v>190</v>
+      </c>
+      <c r="M87">
         <v>876348</v>
       </c>
-      <c r="O87" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
+      <c r="N87" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E88" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F88">
         <v>65.749</v>
       </c>
       <c r="G88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H88">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I88" s="1">
-        <v>1.704</v>
+        <v>112.036</v>
       </c>
       <c r="J88">
-        <v>112.036296</v>
+        <v>1.75</v>
       </c>
       <c r="K88" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L88" s="1">
-        <v>115.06075</v>
-      </c>
-      <c r="M88" t="s">
-        <v>192</v>
-      </c>
-      <c r="N88">
+        <v>115.061</v>
+      </c>
+      <c r="L88" t="s">
+        <v>191</v>
+      </c>
+      <c r="M88">
         <v>876627</v>
       </c>
-      <c r="O88" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+      <c r="N88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F89">
         <v>39.88</v>
       </c>
       <c r="G89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H89">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I89" s="1">
-        <v>1.704</v>
+        <v>67.956</v>
       </c>
       <c r="J89">
-        <v>67.95552000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K89" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L89" s="1">
         <v>69.79000000000001</v>
       </c>
-      <c r="M89" t="s">
-        <v>193</v>
-      </c>
-      <c r="N89">
+      <c r="L89" t="s">
+        <v>192</v>
+      </c>
+      <c r="M89">
         <v>306735</v>
       </c>
-      <c r="O89" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="N89" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B90" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" t="s">
         <v>63</v>
       </c>
-      <c r="C90" t="s">
-        <v>64</v>
-      </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F90">
         <v>46.718</v>
       </c>
       <c r="G90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H90">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I90" s="1">
-        <v>1.704</v>
+        <v>79.607</v>
       </c>
       <c r="J90">
-        <v>79.607472</v>
+        <v>1.77</v>
       </c>
       <c r="K90" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L90" s="1">
-        <v>82.69086</v>
-      </c>
-      <c r="M90" t="s">
-        <v>194</v>
-      </c>
-      <c r="N90">
+        <v>82.691</v>
+      </c>
+      <c r="L90" t="s">
+        <v>193</v>
+      </c>
+      <c r="M90">
         <v>0</v>
       </c>
-      <c r="O90" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15">
+      <c r="N90" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F91">
         <v>45.75</v>
       </c>
       <c r="G91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H91">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I91" s="1">
-        <v>1.704</v>
+        <v>77.958</v>
       </c>
       <c r="J91">
-        <v>77.958</v>
+        <v>1.76</v>
       </c>
       <c r="K91" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L91" s="1">
         <v>80.52</v>
       </c>
-      <c r="M91" t="s">
-        <v>195</v>
-      </c>
-      <c r="N91">
+      <c r="L91" t="s">
+        <v>194</v>
+      </c>
+      <c r="M91">
         <v>343443</v>
       </c>
-      <c r="O91" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+      <c r="N91" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F92">
         <v>78.648</v>
       </c>
       <c r="G92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H92">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I92" s="1">
-        <v>1.704</v>
+        <v>134.016</v>
       </c>
       <c r="J92">
-        <v>134.016192</v>
+        <v>1.76</v>
       </c>
       <c r="K92" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L92" s="1">
-        <v>138.42048</v>
-      </c>
-      <c r="M92" t="s">
-        <v>196</v>
-      </c>
-      <c r="N92">
+        <v>138.42</v>
+      </c>
+      <c r="L92" t="s">
+        <v>195</v>
+      </c>
+      <c r="M92">
         <v>0</v>
       </c>
-      <c r="O92" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15">
+      <c r="N92" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F93">
         <v>23.623</v>
       </c>
       <c r="G93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H93">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I93" s="1">
-        <v>1.704</v>
+        <v>40.254</v>
       </c>
       <c r="J93">
-        <v>40.253592</v>
+        <v>1.75</v>
       </c>
       <c r="K93" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L93" s="1">
-        <v>41.34025</v>
-      </c>
-      <c r="M93" t="s">
-        <v>197</v>
-      </c>
-      <c r="N93">
+        <v>41.34</v>
+      </c>
+      <c r="L93" t="s">
+        <v>196</v>
+      </c>
+      <c r="M93">
         <v>420437</v>
       </c>
-      <c r="O93" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+      <c r="N93" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F94">
         <v>41.8</v>
       </c>
       <c r="G94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H94">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I94" s="1">
-        <v>1.489</v>
+        <v>62.24</v>
       </c>
       <c r="J94">
-        <v>62.2402</v>
+        <v>1.55</v>
       </c>
       <c r="K94" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L94" s="1">
         <v>64.79000000000001</v>
       </c>
-      <c r="M94" t="s">
-        <v>198</v>
-      </c>
-      <c r="N94">
+      <c r="L94" t="s">
+        <v>197</v>
+      </c>
+      <c r="M94">
         <v>16702</v>
       </c>
-      <c r="O94" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15">
+      <c r="N94" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E95" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F95">
         <v>71.961</v>
       </c>
       <c r="G95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H95">
-        <v>1.676</v>
+        <v>1.736</v>
       </c>
       <c r="I95" s="1">
-        <v>1.736</v>
+        <v>124.924</v>
       </c>
       <c r="J95">
-        <v>124.924296</v>
+        <v>1.81</v>
       </c>
       <c r="K95" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L95" s="1">
-        <v>130.24941</v>
-      </c>
-      <c r="M95" t="s">
-        <v>199</v>
-      </c>
-      <c r="N95">
+        <v>130.249</v>
+      </c>
+      <c r="L95" t="s">
+        <v>198</v>
+      </c>
+      <c r="M95">
         <v>0</v>
       </c>
-      <c r="O95" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15">
+      <c r="N95" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F96">
         <v>39.022</v>
       </c>
       <c r="G96" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H96">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I96" s="1">
-        <v>1.704</v>
+        <v>66.49299999999999</v>
       </c>
       <c r="J96">
-        <v>66.493488</v>
+        <v>1.79</v>
       </c>
       <c r="K96" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L96" s="1">
-        <v>69.84938</v>
-      </c>
-      <c r="M96" t="s">
-        <v>200</v>
-      </c>
-      <c r="N96">
+        <v>69.849</v>
+      </c>
+      <c r="L96" t="s">
+        <v>199</v>
+      </c>
+      <c r="M96">
         <v>0</v>
       </c>
-      <c r="O96" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+      <c r="N96" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F97">
         <v>19.881</v>
       </c>
       <c r="G97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H97">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I97" s="1">
-        <v>1.719</v>
+        <v>34.175</v>
       </c>
       <c r="J97">
-        <v>34.175439</v>
+        <v>1.77</v>
       </c>
       <c r="K97" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L97" s="1">
-        <v>35.18937</v>
-      </c>
-      <c r="M97" t="s">
-        <v>201</v>
-      </c>
-      <c r="N97">
+        <v>35.189</v>
+      </c>
+      <c r="L97" t="s">
+        <v>200</v>
+      </c>
+      <c r="M97">
         <v>421075</v>
       </c>
-      <c r="O97" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15">
+      <c r="N97" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F98">
         <v>35.511</v>
       </c>
       <c r="G98" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H98">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I98" s="1">
-        <v>1.719</v>
+        <v>61.043</v>
       </c>
       <c r="J98">
-        <v>61.043409</v>
+        <v>1.78</v>
       </c>
       <c r="K98" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L98" s="1">
-        <v>63.20958</v>
-      </c>
-      <c r="M98" t="s">
-        <v>202</v>
-      </c>
-      <c r="N98">
+        <v>63.21</v>
+      </c>
+      <c r="L98" t="s">
+        <v>201</v>
+      </c>
+      <c r="M98">
         <v>420932</v>
       </c>
-      <c r="O98" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15">
+      <c r="N98" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B99" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F99">
         <v>38.708</v>
       </c>
       <c r="G99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H99">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I99" s="1">
-        <v>1.719</v>
+        <v>66.539</v>
       </c>
       <c r="J99">
-        <v>66.539052</v>
+        <v>1.78</v>
       </c>
       <c r="K99" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L99" s="1">
-        <v>68.90024</v>
-      </c>
-      <c r="M99" t="s">
-        <v>203</v>
-      </c>
-      <c r="N99">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L99" t="s">
+        <v>202</v>
+      </c>
+      <c r="M99">
         <v>0</v>
       </c>
-      <c r="O99" t="s">
+      <c r="N99" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="3" t="s">
         <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
-      <c r="A102" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -6016,149 +5716,149 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:14">
       <c r="A103" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="C103" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="D103" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>305</v>
-      </c>
       <c r="E103" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="6">
         <v>3879.731</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="7">
         <v>67</v>
       </c>
       <c r="D104" s="7">
-        <v>1.544643</v>
-      </c>
-      <c r="E104" s="6">
-        <v>5992.8</v>
-      </c>
-      <c r="F104" s="6">
-        <v>6315.63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+        <v>1.545</v>
+      </c>
+      <c r="E104" s="7">
+        <v>5992.794</v>
+      </c>
+      <c r="F104" s="7">
+        <v>6315.624</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B105" s="6">
         <v>791.104</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="7">
         <v>14</v>
       </c>
       <c r="D105" s="7">
-        <v>1.702724</v>
-      </c>
-      <c r="E105" s="6">
-        <v>1347.03</v>
-      </c>
-      <c r="F105" s="6">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15">
+        <v>1.703</v>
+      </c>
+      <c r="E105" s="7">
+        <v>1347.032</v>
+      </c>
+      <c r="F105" s="7">
+        <v>1496.998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="6">
         <v>624.832</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="7">
         <v>8</v>
       </c>
       <c r="D106" s="7">
-        <v>1.705467</v>
-      </c>
-      <c r="E106" s="6">
+        <v>1.705</v>
+      </c>
+      <c r="E106" s="7">
         <v>1065.63</v>
       </c>
-      <c r="F106" s="6">
-        <v>1114.62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15">
+      <c r="F106" s="7">
+        <v>1114.621</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="6">
         <v>174.734</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="7">
         <v>5</v>
       </c>
       <c r="D107" s="7">
-        <v>1.432809</v>
-      </c>
-      <c r="E107" s="6">
+        <v>1.433</v>
+      </c>
+      <c r="E107" s="7">
         <v>250.36</v>
       </c>
-      <c r="F107" s="6">
-        <v>266.76</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
+      <c r="F107" s="7">
+        <v>266.759</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="6">
         <v>33.948</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="7">
         <v>3</v>
       </c>
       <c r="D108" s="7">
-        <v>1.248934</v>
-      </c>
-      <c r="E108" s="6">
+        <v>1.249</v>
+      </c>
+      <c r="E108" s="7">
         <v>42.4</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="7">
         <v>42.4</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:14">
       <c r="A109" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="6">
         <v>1</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="7">
         <v>1</v>
       </c>
       <c r="D109" s="7">
         <v>10.39</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="7">
         <v>10.39</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="7">
         <v>10.39</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:14">
       <c r="A110" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B110" s="9">
         <v>5505.349</v>
@@ -6168,10 +5868,10 @@
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="9">
-        <v>8708.610000000001</v>
+        <v>8708.606</v>
       </c>
       <c r="F110" s="9">
-        <v>9246.799999999999</v>
+        <v>9246.791999999999</v>
       </c>
     </row>
   </sheetData>
